--- a/Initial Testing and Coding/motor_optimizing_parts/step_test_rpm_data.xlsx
+++ b/Initial Testing and Coding/motor_optimizing_parts/step_test_rpm_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="9" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="21" uniqueCount="3">
   <si>
     <t>time_s</t>
   </si>
@@ -67,11 +67,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="true"/>
-    <col min="2" max="2" width="12.5546875" customWidth="true"/>
+    <col min="2" max="2" width="11.5546875" customWidth="true"/>
     <col min="3" max="3" width="5" customWidth="true"/>
   </cols>
   <sheetData>
@@ -88,7 +88,7 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.0010862000000000001</v>
+        <v>0.00027920000000000001</v>
       </c>
       <c r="B2" s="0">
         <v>0</v>
@@ -99,7 +99,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.76073460000000004</v>
+        <v>0.25053500000000001</v>
       </c>
       <c r="B3" s="0">
         <v>0</v>
@@ -110,563 +110,1201 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>1.1972573</v>
+        <v>0.4362568</v>
       </c>
       <c r="B4" s="0">
         <v>0</v>
       </c>
       <c r="C4" s="0">
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>1.5749283999999999</v>
+        <v>0.63052059999999999</v>
       </c>
       <c r="B5" s="0">
-        <v>0.3877145257568595</v>
+        <v>0</v>
       </c>
       <c r="C5" s="0">
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>2.0159020999999999</v>
+        <v>1.0420240000000001</v>
       </c>
       <c r="B6" s="0">
-        <v>11.637429534451803</v>
+        <v>0</v>
       </c>
       <c r="C6" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>2.6714600000000002</v>
+        <v>1.2830774</v>
       </c>
       <c r="B7" s="0">
-        <v>22.865430792779005</v>
+        <v>6.0819363202154744</v>
       </c>
       <c r="C7" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>2.9818685999999999</v>
+        <v>1.4746598</v>
       </c>
       <c r="B8" s="0">
-        <v>31.565555112157235</v>
+        <v>24.377617876611367</v>
       </c>
       <c r="C8" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>3.3463273999999999</v>
+        <v>1.6046623</v>
       </c>
       <c r="B9" s="0">
-        <v>38.652343761658628</v>
+        <v>39.244348770240009</v>
       </c>
       <c r="C9" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>3.7919995000000002</v>
+        <v>1.8124906999999999</v>
       </c>
       <c r="B10" s="0">
-        <v>43.37763887538668</v>
+        <v>50.295252940334422</v>
       </c>
       <c r="C10" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>4.0139716999999999</v>
+        <v>1.9849383</v>
       </c>
       <c r="B11" s="0">
-        <v>46.893135487152598</v>
+        <v>58.970130404835565</v>
       </c>
       <c r="C11" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>4.4084569</v>
+        <v>2.1509605999999999</v>
       </c>
       <c r="B12" s="0">
-        <v>50.325227352075046</v>
+        <v>64.685262656050554</v>
       </c>
       <c r="C12" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>4.6780917999999998</v>
+        <v>2.3003364999999998</v>
       </c>
       <c r="B13" s="0">
-        <v>52.340377744608745</v>
+        <v>69.494095539618712</v>
       </c>
       <c r="C13" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>4.9840078999999999</v>
+        <v>2.4620264000000001</v>
       </c>
       <c r="B14" s="0">
-        <v>54.350458563558007</v>
+        <v>73.126389404793457</v>
       </c>
       <c r="C14" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>5.3100778999999996</v>
+        <v>2.6240529000000001</v>
       </c>
       <c r="B15" s="0">
-        <v>55.647903660060585</v>
+        <v>75.795950395859194</v>
       </c>
       <c r="C15" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>5.8975909</v>
+        <v>2.7937637</v>
       </c>
       <c r="B16" s="0">
-        <v>56.379980606124974</v>
+        <v>78.101608094323083</v>
       </c>
       <c r="C16" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>6.3516282000000004</v>
+        <v>2.9464616000000001</v>
       </c>
       <c r="B17" s="0">
-        <v>57.049348269215841</v>
+        <v>80.023783280383029</v>
       </c>
       <c r="C17" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>6.7420226000000003</v>
+        <v>3.1057212999999999</v>
       </c>
       <c r="B18" s="0">
-        <v>57.630059301840717</v>
+        <v>81.052662968560895</v>
       </c>
       <c r="C18" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>7.0101528000000002</v>
+        <v>3.2627584999999999</v>
       </c>
       <c r="B19" s="0">
-        <v>57.860955218624426</v>
+        <v>81.405631492696429</v>
       </c>
       <c r="C19" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>7.3329288999999998</v>
+        <v>3.4165972999999998</v>
       </c>
       <c r="B20" s="0">
-        <v>58.593115300865918</v>
+        <v>81.936471790984925</v>
       </c>
       <c r="C20" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>7.6416677999999996</v>
+        <v>3.5724980999999998</v>
       </c>
       <c r="B21" s="0">
-        <v>59.006106694594969</v>
+        <v>82.447847681078443</v>
       </c>
       <c r="C21" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>7.9047552000000003</v>
+        <v>3.7339804999999999</v>
       </c>
       <c r="B22" s="0">
-        <v>59.336477302447094</v>
+        <v>82.824462313335374</v>
       </c>
       <c r="C22" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>8.4283918</v>
+        <v>3.8851521</v>
       </c>
       <c r="B23" s="0">
-        <v>59.688053007101956</v>
+        <v>83.723406339923528</v>
       </c>
       <c r="C23" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>8.7220700000000004</v>
+        <v>4.0516699000000003</v>
       </c>
       <c r="B24" s="0">
-        <v>59.109971310341422</v>
+        <v>83.285859374628913</v>
       </c>
       <c r="C24" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>9.1426558</v>
+        <v>4.2089594000000004</v>
       </c>
       <c r="B25" s="0">
-        <v>59.443205337674016</v>
+        <v>83.501581192691447</v>
       </c>
       <c r="C25" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>9.4360710000000001</v>
+        <v>4.3651438000000002</v>
       </c>
       <c r="B26" s="0">
-        <v>59.706024047479531</v>
+        <v>83.800790126073466</v>
       </c>
       <c r="C26" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>9.7888423000000007</v>
+        <v>4.5320764000000002</v>
       </c>
       <c r="B27" s="0">
-        <v>60.010956323572067</v>
+        <v>83.924110546453903</v>
       </c>
       <c r="C27" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>10.1378424</v>
+        <v>4.6918198000000002</v>
       </c>
       <c r="B28" s="0">
-        <v>59.907926440470135</v>
+        <v>84.093073636039009</v>
       </c>
       <c r="C28" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>10.540825</v>
+        <v>4.8568332999999999</v>
       </c>
       <c r="B29" s="0">
-        <v>60.214305877277646</v>
+        <v>84.366764047281663</v>
       </c>
       <c r="C29" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>10.910540900000001</v>
+        <v>5.0591913000000002</v>
       </c>
       <c r="B30" s="0">
-        <v>60.833960819273898</v>
+        <v>84.312753073526721</v>
       </c>
       <c r="C30" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>11.3553088</v>
+        <v>5.2393337999999998</v>
       </c>
       <c r="B31" s="0">
-        <v>61.637032086019787</v>
+        <v>84.061330916893923</v>
       </c>
       <c r="C31" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>11.7035854</v>
+        <v>5.4162381999999996</v>
       </c>
       <c r="B32" s="0">
-        <v>61.855746609489557</v>
+        <v>84.09247462191567</v>
       </c>
       <c r="C32" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>11.937804399999999</v>
+        <v>5.5938274000000003</v>
       </c>
       <c r="B33" s="0">
-        <v>62.257608327750788</v>
+        <v>84.245836775597837</v>
       </c>
       <c r="C33" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>12.4291123</v>
+        <v>5.7488007000000003</v>
       </c>
       <c r="B34" s="0">
-        <v>62.30387087616576</v>
+        <v>84.305527390822178</v>
       </c>
       <c r="C34" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>12.653389799999999</v>
+        <v>5.9276467000000004</v>
       </c>
       <c r="B35" s="0">
-        <v>63.177550198337649</v>
+        <v>84.047135801295653</v>
       </c>
       <c r="C35" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>13.046017000000001</v>
+        <v>6.0859322999999996</v>
       </c>
       <c r="B36" s="0">
-        <v>63.196964065029405</v>
+        <v>84.786270082681753</v>
       </c>
       <c r="C36" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>13.341593899999999</v>
+        <v>6.2706339</v>
       </c>
       <c r="B37" s="0">
-        <v>63.322996157539613</v>
+        <v>84.008738300892645</v>
       </c>
       <c r="C37" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>13.6386112</v>
+        <v>6.4634711999999999</v>
       </c>
       <c r="B38" s="0">
-        <v>63.406423545876969</v>
+        <v>84.101316734989496</v>
       </c>
       <c r="C38" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>13.989704</v>
+        <v>6.6322906000000001</v>
       </c>
       <c r="B39" s="0">
-        <v>63.18458847783522</v>
+        <v>84.136109449893212</v>
       </c>
       <c r="C39" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>14.3922446</v>
+        <v>7.3576775000000003</v>
       </c>
       <c r="B40" s="0">
-        <v>63.38948927396909</v>
+        <v>84.213968329487017</v>
       </c>
       <c r="C40" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>14.830731200000001</v>
+        <v>9.0546845999999999</v>
       </c>
       <c r="B41" s="0">
-        <v>63.379870850676447</v>
+        <v>84.243812568201634</v>
       </c>
       <c r="C41" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>15.2476755</v>
+        <v>9.2003930999999994</v>
       </c>
       <c r="B42" s="0">
-        <v>63.608478707419678</v>
+        <v>83.539059843912966</v>
       </c>
       <c r="C42" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>15.506751700000001</v>
+        <v>9.3987075000000004</v>
       </c>
       <c r="B43" s="0">
-        <v>62.63577803106395</v>
+        <v>83.931836287607481</v>
       </c>
       <c r="C43" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>15.865116799999999</v>
+        <v>9.5957284000000005</v>
       </c>
       <c r="B44" s="0">
-        <v>62.448883834957442</v>
+        <v>84.230158251662402</v>
       </c>
       <c r="C44" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>16.3795365</v>
+        <v>9.9539535000000008</v>
       </c>
       <c r="B45" s="0">
-        <v>62.415937375786619</v>
+        <v>84.213857842563755</v>
       </c>
       <c r="C45" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>16.6447988</v>
+        <v>10.243491499999999</v>
       </c>
       <c r="B46" s="0">
-        <v>62.281815988511269</v>
+        <v>84.105090500386524</v>
       </c>
       <c r="C46" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>16.996815999999999</v>
+        <v>10.409708800000001</v>
       </c>
       <c r="B47" s="0">
-        <v>62.538510697266546</v>
+        <v>84.328969677435808</v>
       </c>
       <c r="C47" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>17.343680599999999</v>
+        <v>10.6042568</v>
       </c>
       <c r="B48" s="0">
-        <v>62.332917044541375</v>
+        <v>84.128463384893962</v>
       </c>
       <c r="C48" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>17.669041100000001</v>
+        <v>10.789295900000001</v>
       </c>
       <c r="B49" s="0">
-        <v>62.358747360617755</v>
+        <v>84.385284386535034</v>
       </c>
       <c r="C49" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>18.001811700000001</v>
+        <v>10.9533086</v>
       </c>
       <c r="B50" s="0">
-        <v>61.998342022065749</v>
+        <v>84.160604850062825</v>
       </c>
       <c r="C50" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>18.6807591</v>
+        <v>11.1236221</v>
       </c>
       <c r="B51" s="0">
-        <v>62.361020452080822</v>
+        <v>84.278913939116947</v>
       </c>
       <c r="C51" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>19.207685699999999</v>
+        <v>11.3027607</v>
       </c>
       <c r="B52" s="0">
-        <v>62.830876937146591</v>
+        <v>84.20250730520786</v>
       </c>
       <c r="C52" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>19.508813100000001</v>
+        <v>11.470632200000001</v>
       </c>
       <c r="B53" s="0">
-        <v>62.915002426578568</v>
+        <v>84.330920058924747</v>
       </c>
       <c r="C53" s="0">
-        <v>170</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>19.8054299</v>
+        <v>11.6525762</v>
       </c>
       <c r="B54" s="0">
-        <v>63.254362016562865</v>
+        <v>84.300586071856742</v>
       </c>
       <c r="C54" s="0">
-        <v>170</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0">
+        <v>11.801527500000001</v>
+      </c>
+      <c r="B55" s="0">
+        <v>84.217439719622632</v>
+      </c>
+      <c r="C55" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0">
+        <v>11.966531099999999</v>
+      </c>
+      <c r="B56" s="0">
+        <v>84.266515455016929</v>
+      </c>
+      <c r="C56" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0">
+        <v>12.321797999999999</v>
+      </c>
+      <c r="B57" s="0">
+        <v>84.622412263410268</v>
+      </c>
+      <c r="C57" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0">
+        <v>12.474920900000001</v>
+      </c>
+      <c r="B58" s="0">
+        <v>84.831533686373817</v>
+      </c>
+      <c r="C58" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0">
+        <v>12.6610748</v>
+      </c>
+      <c r="B59" s="0">
+        <v>84.075238209716673</v>
+      </c>
+      <c r="C59" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0">
+        <v>12.9383119</v>
+      </c>
+      <c r="B60" s="0">
+        <v>84.241235040395225</v>
+      </c>
+      <c r="C60" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0">
+        <v>13.1098268</v>
+      </c>
+      <c r="B61" s="0">
+        <v>84.118299234899354</v>
+      </c>
+      <c r="C61" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0">
+        <v>13.2840586</v>
+      </c>
+      <c r="B62" s="0">
+        <v>84.335050953741401</v>
+      </c>
+      <c r="C62" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0">
+        <v>13.4466856</v>
+      </c>
+      <c r="B63" s="0">
+        <v>84.54234074655848</v>
+      </c>
+      <c r="C63" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0">
+        <v>13.602970300000001</v>
+      </c>
+      <c r="B64" s="0">
+        <v>84.430658000236278</v>
+      </c>
+      <c r="C64" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0">
+        <v>13.7617242</v>
+      </c>
+      <c r="B65" s="0">
+        <v>84.076139452137312</v>
+      </c>
+      <c r="C65" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0">
+        <v>13.9235273</v>
+      </c>
+      <c r="B66" s="0">
+        <v>84.36828024466385</v>
+      </c>
+      <c r="C66" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0">
+        <v>14.0943763</v>
+      </c>
+      <c r="B67" s="0">
+        <v>84.326544522174501</v>
+      </c>
+      <c r="C67" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0">
+        <v>14.26427</v>
+      </c>
+      <c r="B68" s="0">
+        <v>84.108794793203558</v>
+      </c>
+      <c r="C68" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0">
+        <v>14.5073305</v>
+      </c>
+      <c r="B69" s="0">
+        <v>84.54891449035209</v>
+      </c>
+      <c r="C69" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0">
+        <v>14.6630383</v>
+      </c>
+      <c r="B70" s="0">
+        <v>84.020342411807263</v>
+      </c>
+      <c r="C70" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0">
+        <v>14.8248172</v>
+      </c>
+      <c r="B71" s="0">
+        <v>84.219240411520232</v>
+      </c>
+      <c r="C71" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0">
+        <v>14.996568699999999</v>
+      </c>
+      <c r="B72" s="0">
+        <v>84.509637940430565</v>
+      </c>
+      <c r="C72" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0">
+        <v>15.199975999999999</v>
+      </c>
+      <c r="B73" s="0">
+        <v>84.39039426704295</v>
+      </c>
+      <c r="C73" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0">
+        <v>15.3691569</v>
+      </c>
+      <c r="B74" s="0">
+        <v>84.455687863978767</v>
+      </c>
+      <c r="C74" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0">
+        <v>15.5026349</v>
+      </c>
+      <c r="B75" s="0">
+        <v>84.225357201419811</v>
+      </c>
+      <c r="C75" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0">
+        <v>15.738811399999999</v>
+      </c>
+      <c r="B76" s="0">
+        <v>84.543770620807536</v>
+      </c>
+      <c r="C76" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0">
+        <v>15.8720807</v>
+      </c>
+      <c r="B77" s="0">
+        <v>84.042737881092521</v>
+      </c>
+      <c r="C77" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0">
+        <v>16.017013500000001</v>
+      </c>
+      <c r="B78" s="0">
+        <v>84.815547948583316</v>
+      </c>
+      <c r="C78" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0">
+        <v>16.1837628</v>
+      </c>
+      <c r="B79" s="0">
+        <v>84.333529915952781</v>
+      </c>
+      <c r="C79" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0">
+        <v>16.336540800000002</v>
+      </c>
+      <c r="B80" s="0">
+        <v>84.312454463219098</v>
+      </c>
+      <c r="C80" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0">
+        <v>16.528497000000002</v>
+      </c>
+      <c r="B81" s="0">
+        <v>84.742223523626038</v>
+      </c>
+      <c r="C81" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0">
+        <v>16.705015899999999</v>
+      </c>
+      <c r="B82" s="0">
+        <v>85.205502818038539</v>
+      </c>
+      <c r="C82" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0">
+        <v>16.865708600000001</v>
+      </c>
+      <c r="B83" s="0">
+        <v>84.873610214770054</v>
+      </c>
+      <c r="C83" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0">
+        <v>17.0371123</v>
+      </c>
+      <c r="B84" s="0">
+        <v>84.251945904517811</v>
+      </c>
+      <c r="C84" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0">
+        <v>17.209488499999999</v>
+      </c>
+      <c r="B85" s="0">
+        <v>84.539686169418559</v>
+      </c>
+      <c r="C85" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0">
+        <v>17.4092664</v>
+      </c>
+      <c r="B86" s="0">
+        <v>84.580065512983353</v>
+      </c>
+      <c r="C86" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0">
+        <v>17.534990700000002</v>
+      </c>
+      <c r="B87" s="0">
+        <v>84.34247457732414</v>
+      </c>
+      <c r="C87" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0">
+        <v>17.6980881</v>
+      </c>
+      <c r="B88" s="0">
+        <v>84.398911451439915</v>
+      </c>
+      <c r="C88" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0">
+        <v>17.868862199999999</v>
+      </c>
+      <c r="B89" s="0">
+        <v>84.766557321314849</v>
+      </c>
+      <c r="C89" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0">
+        <v>18.050496899999999</v>
+      </c>
+      <c r="B90" s="0">
+        <v>84.564849980853708</v>
+      </c>
+      <c r="C90" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0">
+        <v>18.244396999999999</v>
+      </c>
+      <c r="B91" s="0">
+        <v>84.761945201830173</v>
+      </c>
+      <c r="C91" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0">
+        <v>18.441696499999999</v>
+      </c>
+      <c r="B92" s="0">
+        <v>84.623572204099872</v>
+      </c>
+      <c r="C92" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0">
+        <v>18.611797200000002</v>
+      </c>
+      <c r="B93" s="0">
+        <v>84.694601121733655</v>
+      </c>
+      <c r="C93" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0">
+        <v>18.783007300000001</v>
+      </c>
+      <c r="B94" s="0">
+        <v>84.975376051695491</v>
+      </c>
+      <c r="C94" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0">
+        <v>18.950597200000001</v>
+      </c>
+      <c r="B95" s="0">
+        <v>84.711742830540345</v>
+      </c>
+      <c r="C95" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0">
+        <v>19.106124000000001</v>
+      </c>
+      <c r="B96" s="0">
+        <v>85.222765461367018</v>
+      </c>
+      <c r="C96" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0">
+        <v>19.270662600000001</v>
+      </c>
+      <c r="B97" s="0">
+        <v>84.55921260594674</v>
+      </c>
+      <c r="C97" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0">
+        <v>19.433580299999999</v>
+      </c>
+      <c r="B98" s="0">
+        <v>85.143787556322309</v>
+      </c>
+      <c r="C98" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0">
+        <v>19.632699299999999</v>
+      </c>
+      <c r="B99" s="0">
+        <v>84.914882651468005</v>
+      </c>
+      <c r="C99" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0">
+        <v>19.802477199999999</v>
+      </c>
+      <c r="B100" s="0">
+        <v>85.258463212729737</v>
+      </c>
+      <c r="C100" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0">
+        <v>19.9724784</v>
+      </c>
+      <c r="B101" s="0">
+        <v>84.479416738301438</v>
+      </c>
+      <c r="C101" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0">
+        <v>19.2109922</v>
+      </c>
+      <c r="B102" s="0">
+        <v>84.564800530292729</v>
+      </c>
+      <c r="C102" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0">
+        <v>19.406760500000001</v>
+      </c>
+      <c r="B103" s="0">
+        <v>84.731588317257845</v>
+      </c>
+      <c r="C103" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0">
+        <v>19.5522077</v>
+      </c>
+      <c r="B104" s="0">
+        <v>84.297506910277761</v>
+      </c>
+      <c r="C104" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0">
+        <v>19.7127427</v>
+      </c>
+      <c r="B105" s="0">
+        <v>84.469053412622657</v>
+      </c>
+      <c r="C105" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0">
+        <v>19.869509900000001</v>
+      </c>
+      <c r="B106" s="0">
+        <v>84.459066144187219</v>
+      </c>
+      <c r="C106" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0">
+        <v>19.029435100000001</v>
+      </c>
+      <c r="B107" s="0">
+        <v>85.157092995470123</v>
+      </c>
+      <c r="C107" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0">
+        <v>19.264889799999999</v>
+      </c>
+      <c r="B108" s="0">
+        <v>85.042654165768241</v>
+      </c>
+      <c r="C108" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0">
+        <v>19.4254085</v>
+      </c>
+      <c r="B109" s="0">
+        <v>85.530680518845713</v>
+      </c>
+      <c r="C109" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0">
+        <v>19.6025107</v>
+      </c>
+      <c r="B110" s="0">
+        <v>84.807994124110849</v>
+      </c>
+      <c r="C110" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0">
+        <v>19.783517199999999</v>
+      </c>
+      <c r="B111" s="0">
+        <v>84.954873750971061</v>
+      </c>
+      <c r="C111" s="0">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0">
+        <v>19.945065700000001</v>
+      </c>
+      <c r="B112" s="0">
+        <v>85.447798044137215</v>
+      </c>
+      <c r="C112" s="0">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
